--- a/database/CB2025-2026.xlsx
+++ b/database/CB2025-2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="28"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Apr" sheetId="1" state="visible" r:id="rId2"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="143">
   <si>
     <t xml:space="preserve">CB2025-2026.xlsx</t>
   </si>
@@ -167,60 +167,6 @@
   </si>
   <si>
     <t xml:space="preserve">C/F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ay18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ay19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ay20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ay21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ay22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ay23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ay24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ay25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cih BF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cih CF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cap Ac BF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cap Ac CF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icici bf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icici cf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inst bf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inst cf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profit%</t>
   </si>
   <si>
     <t xml:space="preserve">NFS/S1ACAG49/CASH WDL/03-05-23                    </t>
@@ -455,6 +401,9 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;= Reciepts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit%</t>
   </si>
   <si>
     <t xml:space="preserve">Income from Proffession</t>
@@ -2263,93 +2212,43 @@
       <c r="Q40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="F41" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H41" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>42</v>
-      </c>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="12"/>
       <c r="N41" s="12"/>
       <c r="O41" s="12"/>
       <c r="P41" s="12"/>
       <c r="Q41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="26" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C42" s="26" t="n">
-        <v>24359</v>
-      </c>
-      <c r="D42" s="26" t="n">
-        <v>27639</v>
-      </c>
-      <c r="E42" s="27" t="n">
-        <v>14139</v>
-      </c>
-      <c r="F42" s="28" t="n">
-        <v>43359</v>
-      </c>
-      <c r="G42" s="26" t="n">
-        <v>10179</v>
-      </c>
-      <c r="H42" s="23" t="n">
-        <v>32399</v>
-      </c>
-      <c r="I42" s="23" t="n">
-        <v>99619</v>
-      </c>
+      <c r="A42" s="25"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
       <c r="N42" s="12"/>
       <c r="O42" s="12"/>
       <c r="P42" s="12"/>
       <c r="Q42" s="12"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="26" t="n">
-        <v>24359</v>
-      </c>
-      <c r="C43" s="26" t="n">
-        <v>27639</v>
-      </c>
-      <c r="D43" s="26" t="n">
-        <v>14139</v>
-      </c>
-      <c r="E43" s="26" t="n">
-        <v>43359</v>
-      </c>
-      <c r="F43" s="27" t="n">
-        <v>10179</v>
-      </c>
-      <c r="G43" s="26" t="n">
-        <v>32399</v>
-      </c>
-      <c r="H43" s="23" t="n">
-        <v>99619</v>
-      </c>
+      <c r="A43" s="25"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="23"/>
       <c r="I43" s="12"/>
       <c r="N43" s="12"/>
       <c r="O43" s="12"/>
@@ -2357,24 +2256,11 @@
       <c r="Q43" s="12"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="10" t="n">
-        <v>30690.41</v>
-      </c>
-      <c r="C44" s="10" t="n">
-        <v>24568.845</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>33675.3625</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>12288.9585</v>
-      </c>
-      <c r="F44" s="23" t="n">
-        <v>33487.764725</v>
-      </c>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="23"/>
       <c r="G44" s="10"/>
       <c r="H44" s="23"/>
       <c r="I44" s="12"/>
@@ -2384,30 +2270,14 @@
       <c r="Q44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45" s="26" t="n">
-        <v>24340</v>
-      </c>
-      <c r="C45" s="26" t="n">
-        <v>49450.41</v>
-      </c>
-      <c r="D45" s="26" t="n">
-        <v>69784.255</v>
-      </c>
-      <c r="E45" s="26" t="n">
-        <v>97259.6225</v>
-      </c>
-      <c r="F45" s="26" t="n">
-        <v>108568.581</v>
-      </c>
-      <c r="G45" s="27" t="n">
-        <v>137816.345725</v>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>194170.34574125</v>
-      </c>
+      <c r="A45" s="25"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="27"/>
       <c r="I45" s="12"/>
       <c r="N45" s="12"/>
       <c r="O45" s="12"/>
@@ -2415,27 +2285,13 @@
       <c r="Q45" s="12"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="26" t="n">
-        <v>49450</v>
-      </c>
-      <c r="C46" s="26" t="n">
-        <v>69784.255</v>
-      </c>
-      <c r="D46" s="26" t="n">
-        <v>97259.6225</v>
-      </c>
-      <c r="E46" s="26" t="n">
-        <v>108568.581</v>
-      </c>
-      <c r="F46" s="27" t="n">
-        <v>137816.345725</v>
-      </c>
-      <c r="G46" s="27" t="n">
-        <v>194170.34574125</v>
-      </c>
+      <c r="A46" s="25"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
       <c r="H46" s="23"/>
       <c r="I46" s="12"/>
       <c r="N46" s="12"/>
@@ -2444,28 +2300,13 @@
       <c r="Q46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="B47" s="10"/>
-      <c r="C47" s="10" t="n">
-        <v>16091.4</v>
-      </c>
-      <c r="D47" s="10" t="n">
-        <v>35041.01</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>80907.01</v>
-      </c>
-      <c r="F47" s="29" t="n">
-        <v>63328.01</v>
-      </c>
-      <c r="G47" s="24" t="n">
-        <v>126038.01</v>
-      </c>
-      <c r="H47" s="24" t="n">
-        <v>160411.91</v>
-      </c>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
       <c r="I47" s="12"/>
       <c r="N47" s="12"/>
       <c r="O47" s="12"/>
@@ -2473,25 +2314,12 @@
       <c r="Q47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="B48" s="22"/>
-      <c r="C48" s="10" t="n">
-        <v>35041.01</v>
-      </c>
-      <c r="D48" s="23" t="n">
-        <v>80907.01</v>
-      </c>
-      <c r="E48" s="23" t="n">
-        <v>63328.01</v>
-      </c>
-      <c r="F48" s="24" t="n">
-        <v>126038.01</v>
-      </c>
-      <c r="G48" s="24" t="n">
-        <v>160411.91</v>
-      </c>
+      <c r="C48" s="10"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
       <c r="H48" s="23"/>
       <c r="I48" s="12"/>
       <c r="N48" s="12"/>
@@ -2500,28 +2328,14 @@
       <c r="Q48" s="12"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="25" t="s">
-        <v>50</v>
-      </c>
+      <c r="A49" s="25"/>
       <c r="B49" s="30"/>
-      <c r="C49" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="30" t="n">
-        <v>2604.25</v>
-      </c>
-      <c r="E49" s="30" t="n">
-        <v>2213.61</v>
-      </c>
-      <c r="F49" s="27" t="n">
-        <v>1881.5685</v>
-      </c>
-      <c r="G49" s="27" t="n">
-        <v>1599.333225</v>
-      </c>
-      <c r="H49" s="23" t="n">
-        <v>1359.43</v>
-      </c>
+      <c r="C49" s="26"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="23"/>
       <c r="I49" s="12"/>
       <c r="N49" s="12"/>
       <c r="O49" s="12"/>
@@ -2529,25 +2343,13 @@
       <c r="Q49" s="12"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="25" t="s">
-        <v>51</v>
-      </c>
+      <c r="A50" s="25"/>
       <c r="B50" s="30"/>
-      <c r="C50" s="26" t="n">
-        <v>2604.25</v>
-      </c>
-      <c r="D50" s="30" t="n">
-        <v>2213.61</v>
-      </c>
-      <c r="E50" s="30" t="n">
-        <v>1881.5685</v>
-      </c>
-      <c r="F50" s="27" t="n">
-        <v>1599.333225</v>
-      </c>
-      <c r="G50" s="23" t="n">
-        <v>1359.43324125</v>
-      </c>
+      <c r="C50" s="26"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="23"/>
       <c r="H50" s="23"/>
       <c r="I50" s="12"/>
       <c r="N50" s="12"/>
@@ -2556,21 +2358,10 @@
       <c r="Q50" s="12"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="10" t="n">
-        <v>55.0007347670251</v>
-      </c>
-      <c r="C51" s="10" t="n">
-        <v>57.741116333725</v>
-      </c>
-      <c r="D51" s="10" t="n">
-        <v>54.1404541800643</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>51.6342794117647</v>
-      </c>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
       <c r="F51" s="23"/>
       <c r="G51" s="23"/>
       <c r="H51" s="23"/>
@@ -2846,7 +2637,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12" t="n">
@@ -2868,7 +2659,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="N8" s="12"/>
       <c r="O8" s="37" t="n">
@@ -2902,7 +2693,7 @@
         <v>45660</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="N9" s="12"/>
       <c r="O9" s="37" t="n">
@@ -3512,7 +3303,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>8</v>
@@ -3536,7 +3327,7 @@
         <v>26</v>
       </c>
       <c r="L29" s="19" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>4</v>
@@ -3574,7 +3365,7 @@
         <v>45682</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L30" s="14" t="s">
         <v>21</v>
@@ -3603,7 +3394,7 @@
         <v>26</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>4</v>
@@ -4124,7 +3915,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="n">
@@ -4145,7 +3936,7 @@
         <v>26</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>11</v>
@@ -4377,7 +4168,7 @@
         <v>28</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12" t="n">
@@ -4399,7 +4190,7 @@
         <v>26</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="12" t="n">
@@ -4433,7 +4224,7 @@
         <v>45701</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L19" s="52" t="s">
         <v>21</v>
@@ -4458,7 +4249,7 @@
         <v>26</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>4</v>
@@ -5449,7 +5240,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>8</v>
@@ -5473,7 +5264,7 @@
         <v>26</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>4</v>
@@ -5512,7 +5303,7 @@
         <v>45721</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L10" s="53" t="s">
         <v>21</v>
@@ -5850,7 +5641,7 @@
         <v>28</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>8</v>
@@ -5874,7 +5665,7 @@
         <v>26</v>
       </c>
       <c r="L21" s="19" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>4</v>
@@ -5900,7 +5691,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>4</v>
@@ -5921,7 +5712,7 @@
         <v>45733</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>21</v>
@@ -6478,19 +6269,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6498,7 +6289,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>1</v>
@@ -6509,7 +6300,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>2</v>
@@ -6520,7 +6311,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>3</v>
@@ -6531,7 +6322,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>4</v>
@@ -6542,7 +6333,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>5</v>
@@ -6553,7 +6344,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>6</v>
@@ -6564,7 +6355,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>7</v>
@@ -6597,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>10</v>
@@ -6608,7 +6399,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>11</v>
@@ -6619,7 +6410,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>12</v>
@@ -6630,7 +6421,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>13</v>
@@ -6641,7 +6432,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>14</v>
@@ -6687,17 +6478,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6711,22 +6502,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -6740,7 +6531,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D6" s="55" t="n">
         <v>4</v>
@@ -6759,7 +6550,7 @@
         <v>45382</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>34</v>
@@ -6816,17 +6607,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6840,22 +6631,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -6866,7 +6657,7 @@
         <v>45382</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
@@ -6885,7 +6676,7 @@
         <v>45382</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>34</v>
@@ -6922,8 +6713,8 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="5.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="15.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="5.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="15.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="55" width="9.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="12" width="11.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="9.06"/>
@@ -6942,17 +6733,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6966,22 +6757,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -6992,10 +6783,10 @@
         <v>45382</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D6" s="55" t="n">
         <v>2</v>
@@ -7014,10 +6805,10 @@
         <v>45382</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D7" s="55" t="n">
         <v>1</v>
@@ -7036,7 +6827,7 @@
         <v>45382</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>34</v>
@@ -7094,17 +6885,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7118,22 +6909,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -7144,7 +6935,7 @@
         <v>45017</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
@@ -8012,7 +7803,7 @@
         <v>45382</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>34</v>
@@ -8074,18 +7865,18 @@
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8103,22 +7894,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -8129,7 +7920,7 @@
         <v>44652</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>20</v>
@@ -8147,7 +7938,7 @@
         <v>44653</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C7" s="22" t="n">
         <v>0</v>
@@ -8168,10 +7959,10 @@
         <v>45016</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F8" s="23" t="n">
         <f aca="false">(Inst!H7-Inst!H7)*0.075</f>
@@ -8187,10 +7978,10 @@
         <v>45016</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F9" s="23" t="n">
         <f aca="false">H8*0.15</f>
@@ -8206,7 +7997,7 @@
         <v>45016</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>34</v>
@@ -8264,17 +8055,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8288,22 +8079,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -8414,7 +8205,7 @@
         <v>45382</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>34</v>
@@ -8656,7 +8447,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>4</v>
@@ -9241,7 +9032,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="12" t="n">
@@ -9263,7 +9054,7 @@
         <v>26</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>9</v>
@@ -9289,7 +9080,7 @@
         <v>28</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
@@ -9298,7 +9089,7 @@
         <v>92839</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L28" s="35"/>
       <c r="N28" s="12"/>
@@ -9333,7 +9124,7 @@
         <v>26</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N29" s="12"/>
       <c r="O29" s="12" t="n">
@@ -9365,7 +9156,7 @@
         <v>45434</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L30" s="31"/>
       <c r="N30" s="12"/>
@@ -9535,7 +9326,7 @@
         <v>26</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>4</v>
@@ -9713,17 +9504,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9737,22 +9528,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -9788,7 +9579,7 @@
         <v>45382</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>34</v>
@@ -9845,17 +9636,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9869,22 +9660,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -9895,10 +9686,10 @@
         <v>45382</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D6" s="55" t="n">
         <v>3</v>
@@ -9917,7 +9708,7 @@
         <v>45382</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>34</v>
@@ -9977,14 +9768,14 @@
         <v>28</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9998,22 +9789,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -10449,7 +10240,7 @@
         <v>45382</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>34</v>
@@ -10509,14 +10300,14 @@
         <v>22</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10530,22 +10321,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -11156,7 +10947,7 @@
         <v>45382</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>34</v>
@@ -11213,17 +11004,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11237,22 +11028,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -11694,7 +11485,7 @@
         <v>45382</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>34</v>
@@ -11752,17 +11543,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11776,22 +11567,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -12277,7 +12068,7 @@
         <v>45382</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>34</v>
@@ -12330,18 +12121,18 @@
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12359,22 +12150,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -12392,10 +12183,10 @@
         <v>45016</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D6" s="55" t="n">
         <v>5</v>
@@ -12416,10 +12207,10 @@
         <v>45016</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D7" s="55" t="n">
         <v>5</v>
@@ -12440,7 +12231,7 @@
         <v>45016</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>34</v>
@@ -12500,17 +12291,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12524,22 +12315,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -12550,10 +12341,10 @@
         <v>45382</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="D6" s="55" t="n">
         <v>13</v>
@@ -12597,7 +12388,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D8" s="55" t="n">
         <v>6</v>
@@ -12619,7 +12410,7 @@
         <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D9" s="55" t="n">
         <v>11</v>
@@ -12660,10 +12451,10 @@
         <v>45382</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D11" s="55" t="n">
         <v>5</v>
@@ -12682,7 +12473,7 @@
         <v>45382</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>34</v>
@@ -12701,7 +12492,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="58" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E14" s="12" t="n">
         <f aca="false">SUM(E6:E11)</f>
@@ -12712,12 +12503,12 @@
         <v>23624</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="5" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="E16" s="59" t="n">
         <f aca="false">E12/F14</f>
@@ -12764,17 +12555,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12788,22 +12579,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -12814,7 +12605,7 @@
         <v>45017</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
@@ -12832,10 +12623,10 @@
         <v>45382</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="D7" s="55" t="n">
         <v>12</v>
@@ -12854,10 +12645,10 @@
         <v>45382</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D8" s="55" t="n">
         <v>10</v>
@@ -12876,7 +12667,7 @@
         <v>45382</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>34</v>
@@ -13151,17 +12942,17 @@
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="56" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H2" s="56" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13175,22 +12966,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E4" s="56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H4" s="56" t="s">
         <v>19</v>
@@ -13201,10 +12992,10 @@
         <v>45382</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="D6" s="55" t="n">
         <v>7</v>
@@ -13217,7 +13008,7 @@
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="57"/>
       <c r="C7" s="2" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="E7" s="12" t="n">
         <f aca="false">BkAc!F7</f>
@@ -13231,7 +13022,7 @@
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="57"/>
       <c r="C8" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="E8" s="12" t="n">
         <f aca="false">CiH!F7</f>
@@ -13245,7 +13036,7 @@
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="57"/>
       <c r="C9" s="2" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="E9" s="12" t="n">
         <f aca="false">Inst!F10</f>
@@ -13261,10 +13052,10 @@
         <v>45382</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D10" s="55" t="n">
         <v>13</v>
@@ -13290,17 +13081,17 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="58" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="C15" s="58" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="59" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F15" s="59"/>
       <c r="G15" s="59"/>
@@ -13310,7 +13101,7 @@
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="58"/>
       <c r="B16" s="58" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C16" s="58"/>
       <c r="D16" s="5"/>
@@ -13324,7 +13115,7 @@
       <c r="A17" s="58"/>
       <c r="B17" s="58"/>
       <c r="C17" s="58" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="59"/>
@@ -13336,13 +13127,13 @@
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="67"/>
       <c r="B18" s="68" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C18" s="69"/>
       <c r="D18" s="70"/>
       <c r="E18" s="23"/>
       <c r="F18" s="71" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="G18" s="72"/>
       <c r="H18" s="72"/>
@@ -13363,10 +13154,10 @@
         <v>45016</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D20" s="65" t="n">
         <f aca="false">CapAc!E9</f>
@@ -13374,10 +13165,10 @@
       </c>
       <c r="E20" s="23"/>
       <c r="F20" s="23" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="H20" s="23"/>
       <c r="I20" s="22" t="n">
@@ -13389,20 +13180,20 @@
         <v>45016</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="D21" s="55" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="23"/>
       <c r="F21" s="23" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="H21" s="23"/>
       <c r="I21" s="22"/>
@@ -13412,20 +13203,20 @@
         <v>45016</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D22" s="55" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="23"/>
       <c r="F22" s="23" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="H22" s="23"/>
       <c r="I22" s="22"/>
@@ -13435,21 +13226,21 @@
         <v>45016</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="D23" s="55" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="23"/>
       <c r="F23" s="23" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="I23" s="22" t="n">
         <v>0</v>
@@ -13464,11 +13255,11 @@
       <c r="C24" s="22"/>
       <c r="E24" s="23"/>
       <c r="F24" s="23" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G24" s="23"/>
       <c r="H24" s="23" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I24" s="23" t="n">
         <f aca="false">BkAc!F7</f>
@@ -13484,11 +13275,11 @@
       <c r="C25" s="22"/>
       <c r="E25" s="23"/>
       <c r="F25" s="23" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="G25" s="23"/>
       <c r="H25" s="23" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="I25" s="22" t="n">
         <v>0</v>
@@ -13504,11 +13295,11 @@
       <c r="C26" s="22"/>
       <c r="E26" s="23"/>
       <c r="F26" s="23" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="G26" s="23"/>
       <c r="H26" s="23" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="I26" s="23" t="n">
         <f aca="false">CiH!F7</f>
@@ -13524,10 +13315,10 @@
       <c r="C27" s="22"/>
       <c r="E27" s="23"/>
       <c r="F27" s="23" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="H27" s="23"/>
       <c r="I27" s="22"/>
@@ -13541,11 +13332,11 @@
       <c r="C28" s="22"/>
       <c r="E28" s="23"/>
       <c r="F28" s="23" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="G28" s="23"/>
       <c r="H28" s="23" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="I28" s="22" t="n">
         <v>0</v>
@@ -13559,11 +13350,11 @@
       <c r="C29" s="22"/>
       <c r="E29" s="23"/>
       <c r="F29" s="23" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="23" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="I29" s="22" t="n">
         <v>0</v>
@@ -13577,10 +13368,10 @@
       <c r="C30" s="22"/>
       <c r="E30" s="23"/>
       <c r="F30" s="23" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="H30" s="23"/>
       <c r="I30" s="22" t="n">
@@ -13595,10 +13386,10 @@
       <c r="C31" s="22"/>
       <c r="E31" s="23"/>
       <c r="F31" s="23" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="G31" s="23" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="H31" s="23"/>
       <c r="I31" s="23" t="n">
@@ -13615,10 +13406,10 @@
       <c r="C32" s="22"/>
       <c r="E32" s="23"/>
       <c r="F32" s="23" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="H32" s="23"/>
       <c r="I32" s="22" t="n">
@@ -13873,7 +13664,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>1</v>
@@ -13895,7 +13686,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N7" s="12"/>
       <c r="O7" s="12" t="n">
@@ -13929,7 +13720,7 @@
         <v>45444</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="N8" s="12"/>
       <c r="O8" s="37" t="n">
@@ -14682,7 +14473,7 @@
         <v>26</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>4</v>
@@ -15104,7 +14895,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="n">
@@ -15126,7 +14917,7 @@
         <v>26</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="37" t="n">
@@ -15160,7 +14951,7 @@
         <v>45478</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="N11" s="12"/>
       <c r="O11" s="37" t="n">
@@ -15183,7 +14974,7 @@
         <v>28</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12" t="n">
@@ -15205,7 +14996,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12" t="n">
@@ -15238,7 +15029,7 @@
         <v>45478</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="N13" s="12"/>
       <c r="O13" s="12" t="n">
@@ -15706,7 +15497,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12" t="n">
@@ -15728,7 +15519,7 @@
         <v>26</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>4</v>
@@ -15765,7 +15556,7 @@
         <v>45497</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>10</v>
@@ -15791,7 +15582,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="12" t="n">
@@ -15813,7 +15604,7 @@
         <v>26</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>4</v>
@@ -15848,7 +15639,7 @@
         <v>45497</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>10</v>
@@ -15939,7 +15730,7 @@
         <v>26</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>4</v>
@@ -16845,7 +16636,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D27" s="43" t="n">
         <v>8</v>
@@ -16871,7 +16662,7 @@
         <v>26</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="M27" s="43" t="n">
         <v>4</v>
@@ -16911,7 +16702,7 @@
         <v>45526</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="44" t="n">
@@ -16938,7 +16729,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>8</v>
@@ -16962,7 +16753,7 @@
         <v>26</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>4</v>
@@ -16998,7 +16789,7 @@
         <v>45527</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>10</v>
@@ -17120,7 +16911,7 @@
         <v>26</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>4</v>
@@ -17910,7 +17701,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>4</v>
@@ -18593,7 +18384,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>8</v>
@@ -18618,7 +18409,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>4</v>
@@ -18655,7 +18446,7 @@
         <v>45568</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L9" s="31"/>
       <c r="M9" s="2" t="n">
@@ -18682,7 +18473,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>8</v>
@@ -18707,7 +18498,7 @@
         <v>26</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>4</v>
@@ -18744,7 +18535,7 @@
         <v>45568</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L11" s="31"/>
       <c r="M11" s="2" t="n">
@@ -18771,7 +18562,7 @@
         <v>28</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>8</v>
@@ -18796,7 +18587,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>4</v>
@@ -18832,7 +18623,7 @@
         <v>45568</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L13" s="35"/>
       <c r="M13" s="2" t="n">
@@ -19269,7 +19060,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>4</v>
@@ -19999,7 +19790,7 @@
         <v>28</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12" t="n">
@@ -20020,7 +19811,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12" t="n">
@@ -20380,7 +20171,7 @@
         <v>45615</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="N24" s="12"/>
       <c r="O24" s="12"/>
@@ -20551,7 +20342,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12" t="n">
@@ -20573,7 +20364,7 @@
         <v>26</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="N30" s="12"/>
       <c r="O30" s="12" t="n">
@@ -20607,7 +20398,7 @@
         <v>45621</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="N31" s="12"/>
       <c r="O31" s="12" t="n">
@@ -20630,7 +20421,7 @@
         <v>28</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12" t="n">
@@ -20652,7 +20443,7 @@
         <v>26</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="N32" s="12"/>
       <c r="O32" s="12" t="n">
@@ -20686,7 +20477,7 @@
         <v>45622</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L33" s="16"/>
       <c r="N33" s="12"/>
@@ -20710,7 +20501,7 @@
         <v>28</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="G34" s="12" t="n">
         <f aca="false">SUM(E34:F34)</f>
@@ -20731,7 +20522,7 @@
         <v>26</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="N34" s="12"/>
       <c r="O34" s="12" t="n">
@@ -20766,7 +20557,7 @@
         <v>45622</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="N35" s="12"/>
       <c r="O35" s="12" t="n">
@@ -20789,7 +20580,7 @@
         <v>28</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="G36" s="12" t="n">
         <f aca="false">SUM(E36:F36)</f>
@@ -20806,7 +20597,7 @@
         <v>26</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>5400</v>
@@ -20838,7 +20629,7 @@
         <v>45625</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>540</v>
@@ -21558,7 +21349,7 @@
         <v>28</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12" t="n">
@@ -21579,7 +21370,7 @@
         <v>26</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="12" t="n">
@@ -21872,7 +21663,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>8</v>
@@ -21896,7 +21687,7 @@
         <v>26</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>4</v>
@@ -22016,7 +21807,7 @@
         <v>26</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>4</v>
